--- a/SGC-CKN/Excel/d085d3d3-0132-4a53-a75c-4e3b70d84ff2_CT-02_P7-137_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/d085d3d3-0132-4a53-a75c-4e3b70d84ff2_CT-02_P7-137_D800_09-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>Dự án</t>
   </si>
@@ -98,7 +98,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">10:11
+    <t xml:space="preserve">10:00
 09/04/2026</t>
   </si>
   <si>
@@ -132,10 +132,6 @@
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">11:55
-09/04/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">13:49
 09/04/2026</t>
   </si>
@@ -219,7 +215,7 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:08
+    <t xml:space="preserve">16:58
 09/04/2026</t>
   </si>
   <si>
@@ -237,7 +233,7 @@
 09/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18:52
+    <t xml:space="preserve">18:32
 09/04/2026</t>
   </si>
   <si>
@@ -1245,19 +1241,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.02</v>
       </c>
       <c r="H11" s="5">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="I11" s="5">
-        <v>5.27</v>
+        <v>7.02</v>
       </c>
       <c r="J11" s="8">
-        <v>4.22</v>
+        <v>4.9</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1309,10 +1305,10 @@
         <v>37</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="F13" s="13">
         <v>-9.02</v>
@@ -1321,33 +1317,33 @@
         <v>-17.22</v>
       </c>
       <c r="H13" s="13">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="I13" s="13">
         <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>4.32</v>
+        <v>3.67</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>43</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>44</v>
       </c>
       <c r="F14" s="16">
         <v>-17.22</v>
@@ -1370,19 +1366,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>47</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>48</v>
       </c>
       <c r="F15" s="19">
         <v>-21.52</v>
@@ -1405,19 +1401,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>51</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>52</v>
       </c>
       <c r="F16" s="22">
         <v>-26.52</v>
@@ -1440,19 +1436,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>55</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>56</v>
       </c>
       <c r="F17" s="25">
         <v>-36.52</v>
@@ -1475,19 +1471,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="30" t="s">
         <v>59</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>60</v>
       </c>
       <c r="F18" s="28">
         <v>-38.2</v>
@@ -1510,34 +1506,34 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>63</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>64</v>
       </c>
       <c r="F19" s="31">
         <v>-39.52</v>
       </c>
       <c r="G19" s="31">
-        <v>-45.52</v>
+        <v>-43.52</v>
       </c>
       <c r="H19" s="31">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="I19" s="31">
-        <v>6</v>
-      </c>
-      <c r="J19" s="12">
-        <v>5.81</v>
+        <v>4</v>
+      </c>
+      <c r="J19" s="8">
+        <v>3.33</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>35</v>
@@ -1545,34 +1541,34 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>68</v>
-      </c>
       <c r="F20" s="34">
-        <v>-45.52</v>
+        <v>-43.52</v>
       </c>
       <c r="G20" s="34">
-        <v>-49.72</v>
+        <v>-44.73</v>
       </c>
       <c r="H20" s="34">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="I20" s="34">
-        <v>4.2</v>
-      </c>
-      <c r="J20" s="12">
-        <v>6.15</v>
+        <v>1.21</v>
+      </c>
+      <c r="J20" s="8">
+        <v>3.46</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>35</v>
@@ -1580,7 +1576,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1686,31 +1682,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1727,19 +1723,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.02</v>
       </c>
       <c r="G2" s="5">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="H2" s="5">
-        <v>5.27</v>
+        <v>7.02</v>
       </c>
       <c r="I2" s="8">
-        <v>4.22</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1791,13 +1787,13 @@
         <v>-17.22</v>
       </c>
       <c r="G4" s="13">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="H4" s="13">
         <v>8.2</v>
       </c>
       <c r="I4" s="8">
-        <v>4.32</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1808,7 +1804,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1837,7 +1833,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1866,7 +1862,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1895,7 +1891,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1924,7 +1920,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1953,7 +1949,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1962,16 +1958,16 @@
         <v>-39.52</v>
       </c>
       <c r="F10" s="31">
-        <v>-45.52</v>
+        <v>-43.52</v>
       </c>
       <c r="G10" s="31">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="H10" s="31">
-        <v>6</v>
-      </c>
-      <c r="I10" s="12">
-        <v>5.81</v>
+        <v>4</v>
+      </c>
+      <c r="I10" s="8">
+        <v>3.33</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1982,30 +1978,30 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>-45.52</v>
+        <v>-43.52</v>
       </c>
       <c r="F11" s="34">
-        <v>-49.72</v>
+        <v>-44.73</v>
       </c>
       <c r="G11" s="34">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
       <c r="H11" s="34">
-        <v>4.2</v>
-      </c>
-      <c r="I11" s="12">
-        <v>6.15</v>
+        <v>1.21</v>
+      </c>
+      <c r="I11" s="8">
+        <v>3.46</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>35</v>
@@ -2017,19 +2013,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-49.72</v>
+        <v>-44.73</v>
       </c>
       <c r="G12" s="39">
-        <v>8.05</v>
+        <v>8.4</v>
       </c>
       <c r="H12" s="39">
-        <v>47.97</v>
+        <v>44.73</v>
       </c>
       <c r="I12" s="39">
-        <v>5.96</v>
+        <v>5.33</v>
       </c>
     </row>
   </sheetData>
